--- a/output/Homeoffice_zaehler.xlsx
+++ b/output/Homeoffice_zaehler.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.15"/>
   <sheetData>
     <row r="1">
@@ -463,6 +463,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>6€</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -480,6 +485,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6€</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -497,6 +507,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6€</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -514,6 +529,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6€</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -531,6 +551,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6€</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -548,6 +573,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6€</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -565,6 +595,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6€</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -580,6 +615,11 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6€</t>
         </is>
       </c>
     </row>

--- a/output/Homeoffice_zaehler.xlsx
+++ b/output/Homeoffice_zaehler.xlsx
@@ -444,35 +444,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A2:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vorbereitungstag </t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>6€</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,7 +472,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -516,7 +494,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -538,7 +516,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -560,7 +538,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -582,7 +560,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -604,20 +582,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vorbereitungstag </t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6€</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vorbereitungstag </t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vorbereitungstag </t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>6€</t>
         </is>

--- a/output/Homeoffice_zaehler.xlsx
+++ b/output/Homeoffice_zaehler.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:D9"/>
+  <dimension ref="A2:D10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.15"/>
   <sheetData>
     <row r="2">
@@ -538,7 +538,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -560,7 +560,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -582,7 +582,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -604,20 +604,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vorbereitungstag </t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6€</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vorbereitungstag </t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vorbereitungstag </t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>6€</t>
         </is>

--- a/output/Homeoffice_zaehler.xlsx
+++ b/output/Homeoffice_zaehler.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:D10"/>
+  <dimension ref="A2:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.15"/>
   <sheetData>
     <row r="2">
@@ -582,7 +582,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -618,28 +618,6 @@
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>6€</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vorbereitungstag </t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
         <is>
           <t>6€</t>
         </is>

--- a/output/Homeoffice_zaehler.xlsx
+++ b/output/Homeoffice_zaehler.xlsx
@@ -444,13 +444,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:D9"/>
+  <dimension ref="A2:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.15"/>
   <sheetData>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,7 +472,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -494,7 +494,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -516,7 +516,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,94 +530,6 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>6€</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vorbereitungstag </t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>6€</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vorbereitungstag </t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>6€</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vorbereitungstag </t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>6€</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vorbereitungstag </t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
         <is>
           <t>6€</t>
         </is>
